--- a/docs/downloads/05/tbl_rev_negatif_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_rev_negatif_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2">
@@ -403,7 +403,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3">
@@ -422,7 +422,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B4">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B5">
@@ -460,7 +460,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B6">
